--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_BASKONIA VITORIA-GASTEIZ.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_BASKONIA VITORIA-GASTEIZ.xlsx
@@ -671,13 +671,13 @@
         <v>0.2329545454545454</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>126</v>
       </c>
       <c r="M2" t="n">
         <v>129</v>
@@ -752,13 +752,13 @@
         <v>0.9839228295819936</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.01515151515151515</v>
+        <v>0.7575757575757576</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.137931034482759</v>
       </c>
       <c r="AM2" t="n">
-        <v>1</v>
+        <v>1.68</v>
       </c>
       <c r="AN2" t="n">
         <v>1.555555555555556</v>
@@ -801,13 +801,13 @@
         <v>0.2329545454545454</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1818181818181818</v>
+        <v>9.090909090909092</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1818181818181818</v>
+        <v>11.45454545454546</v>
       </c>
       <c r="M3" t="n">
         <v>11.72727272727273</v>
@@ -882,13 +882,13 @@
         <v>0.9839228295819936</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.01515151515151515</v>
+        <v>0.7575757575757577</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.137931034482759</v>
       </c>
       <c r="AM3" t="n">
-        <v>1</v>
+        <v>1.68</v>
       </c>
       <c r="AN3" t="n">
         <v>1.555555555555555</v>
@@ -931,13 +931,13 @@
         <v>0.2580213903743315</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>159</v>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>105</v>
       </c>
       <c r="M4" t="n">
         <v>114</v>
@@ -1012,13 +1012,13 @@
         <v>1.191919191919192</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.02027027027027027</v>
+        <v>1.074324324324324</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.5</v>
+        <v>1.842105263157895</v>
       </c>
       <c r="AN4" t="n">
         <v>1.537878787878788</v>
@@ -1061,13 +1061,13 @@
         <v>0.2580213903743316</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7272727272727273</v>
+        <v>9.545454545454545</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2727272727272727</v>
+        <v>14.45454545454546</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4545454545454545</v>
+        <v>9.545454545454545</v>
       </c>
       <c r="M5" t="n">
         <v>10.36363636363636</v>
@@ -1142,13 +1142,13 @@
         <v>1.191919191919192</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.02027027027027027</v>
+        <v>1.074324324324324</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.5</v>
+        <v>1.842105263157895</v>
       </c>
       <c r="AN5" t="n">
         <v>1.537878787878788</v>
@@ -1486,16 +1486,16 @@
         <v>15</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="n">
         <v>1</v>
@@ -1654,13 +1654,13 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="n">
         <v>16</v>
@@ -1816,16 +1816,16 @@
         <v>68</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y10" t="n">
         <v>18</v>
@@ -1981,16 +1981,16 @@
         <v>77</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y11" t="n">
         <v>16</v>
@@ -2146,7 +2146,7 @@
         <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -2311,16 +2311,16 @@
         <v>168</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Y13" t="n">
         <v>73</v>
@@ -2476,16 +2476,16 @@
         <v>37</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y14" t="n">
         <v>17</v>
@@ -2641,16 +2641,16 @@
         <v>107</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y15" t="n">
         <v>23</v>
@@ -2806,16 +2806,16 @@
         <v>210</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Y16" t="n">
         <v>51</v>
@@ -2971,16 +2971,16 @@
         <v>108</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y17" t="n">
         <v>31</v>
@@ -3139,13 +3139,13 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="n">
         <v>24</v>
@@ -3469,13 +3469,13 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
         <v>22</v>
@@ -3631,16 +3631,16 @@
         <v>40</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y21" t="n">
         <v>6</v>
@@ -3964,7 +3964,7 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -4126,16 +4126,16 @@
         <v>42</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y24" t="n">
         <v>14</v>
@@ -4456,16 +4456,16 @@
         <v>1126</v>
       </c>
       <c r="U26" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="W26" t="n">
-        <v>2</v>
+        <v>126</v>
       </c>
       <c r="X26" t="n">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="Y26" t="n">
         <v>315</v>
@@ -4621,16 +4621,16 @@
         <v>1237</v>
       </c>
       <c r="U27" t="n">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="V27" t="n">
-        <v>3</v>
+        <v>159</v>
       </c>
       <c r="W27" t="n">
-        <v>5</v>
+        <v>105</v>
       </c>
       <c r="X27" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="Y27" t="n">
         <v>335</v>
@@ -4845,16 +4845,16 @@
         <v>15</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="Y29" t="n">
         <v>0.167</v>
@@ -5013,13 +5013,13 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="Y30" t="n">
         <v>1.6</v>
@@ -5175,16 +5175,16 @@
         <v>68</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="Y31" t="n">
         <v>3</v>
@@ -5340,16 +5340,16 @@
         <v>77</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.273</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>0.636</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>0.455</v>
       </c>
       <c r="Y32" t="n">
         <v>1.455</v>
@@ -5505,7 +5505,7 @@
         <v>3</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -5670,16 +5670,16 @@
         <v>168</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.545</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.091</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2.364</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.545</v>
       </c>
       <c r="Y34" t="n">
         <v>6.636</v>
@@ -5835,16 +5835,16 @@
         <v>37</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>0.857</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>0.857</v>
       </c>
       <c r="Y35" t="n">
         <v>2.429</v>
@@ -6000,16 +6000,16 @@
         <v>107</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>0.636</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.364</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>0.636</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>0.364</v>
       </c>
       <c r="Y36" t="n">
         <v>2.091</v>
@@ -6165,16 +6165,16 @@
         <v>210</v>
       </c>
       <c r="U37" t="n">
-        <v>0.182</v>
+        <v>1.727</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>2.818</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.636</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
         <v>4.636</v>
@@ -6330,16 +6330,16 @@
         <v>108</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.273</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>0.455</v>
       </c>
       <c r="W38" t="n">
-        <v>0.182</v>
+        <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>0.182</v>
+        <v>0.636</v>
       </c>
       <c r="Y38" t="n">
         <v>2.818</v>
@@ -6498,13 +6498,13 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y39" t="n">
         <v>6</v>
@@ -6828,13 +6828,13 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.273</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="Y41" t="n">
         <v>2</v>
@@ -6990,16 +6990,16 @@
         <v>40</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>0.273</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>0.909</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>0.455</v>
       </c>
       <c r="Y42" t="n">
         <v>0.545</v>
@@ -7323,7 +7323,7 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
@@ -7485,16 +7485,16 @@
         <v>42</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="Y45" t="n">
         <v>2.8</v>
@@ -7815,16 +7815,16 @@
         <v>1126</v>
       </c>
       <c r="U47" t="n">
-        <v>0.182</v>
+        <v>9.090999999999999</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W47" t="n">
-        <v>0.182</v>
+        <v>11.455</v>
       </c>
       <c r="X47" t="n">
-        <v>0.182</v>
+        <v>6.818</v>
       </c>
       <c r="Y47" t="n">
         <v>28.636</v>
@@ -7980,16 +7980,16 @@
         <v>1237</v>
       </c>
       <c r="U48" t="n">
-        <v>0.727</v>
+        <v>9.545</v>
       </c>
       <c r="V48" t="n">
-        <v>0.273</v>
+        <v>14.455</v>
       </c>
       <c r="W48" t="n">
-        <v>0.455</v>
+        <v>9.545</v>
       </c>
       <c r="X48" t="n">
-        <v>0.182</v>
+        <v>5.182</v>
       </c>
       <c r="Y48" t="n">
         <v>30.455</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_BASKONIA VITORIA-GASTEIZ.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_BASKONIA VITORIA-GASTEIZ.xlsx
@@ -683,13 +683,13 @@
         <v>447</v>
       </c>
       <c r="N2" t="n">
-        <v>1143</v>
+        <v>490</v>
       </c>
       <c r="O2" t="n">
-        <v>1298</v>
+        <v>645</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5293637846655791</v>
+        <v>0.2630505709624796</v>
       </c>
       <c r="Q2" t="n">
         <v>275</v>
@@ -710,25 +710,25 @@
         <v>0.03507340946166395</v>
       </c>
       <c r="W2" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="X2" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.02773246329526917</v>
+        <v>0.03588907014681892</v>
       </c>
       <c r="Z2" t="n">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.4078303425774878</v>
+        <v>0.399673735725938</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8805855161787365</v>
+        <v>0.7596899224806202</v>
       </c>
       <c r="AD2" t="n">
         <v>0.4211332312404288</v>
@@ -737,13 +737,13 @@
         <v>0.4418604651162791</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.4431818181818182</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.338</v>
+        <v>0.3336734693877551</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.761171032357473</v>
+        <v>1.51937984496124</v>
       </c>
       <c r="AI2" t="n">
         <v>0.8837209302325582</v>
@@ -813,13 +813,13 @@
         <v>11.76315789473684</v>
       </c>
       <c r="N3" t="n">
-        <v>30.07894736842105</v>
+        <v>12.89473684210526</v>
       </c>
       <c r="O3" t="n">
-        <v>34.1578947368421</v>
+        <v>16.97368421052632</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5293637846655791</v>
+        <v>0.2630505709624796</v>
       </c>
       <c r="Q3" t="n">
         <v>7.236842105263158</v>
@@ -840,25 +840,25 @@
         <v>0.03507340946166394</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7368421052631579</v>
+        <v>1.026315789473684</v>
       </c>
       <c r="X3" t="n">
-        <v>1.789473684210526</v>
+        <v>2.315789473684211</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.02773246329526917</v>
+        <v>0.03588907014681893</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.894736842105264</v>
+        <v>8.605263157894736</v>
       </c>
       <c r="AA3" t="n">
-        <v>26.31578947368421</v>
+        <v>25.78947368421053</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.4078303425774877</v>
+        <v>0.399673735725938</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8805855161787366</v>
+        <v>0.7596899224806202</v>
       </c>
       <c r="AD3" t="n">
         <v>0.4211332312404287</v>
@@ -867,13 +867,13 @@
         <v>0.4418604651162791</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.4431818181818182</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.338</v>
+        <v>0.3336734693877551</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.761171032357473</v>
+        <v>1.51937984496124</v>
       </c>
       <c r="AI3" t="n">
         <v>0.8837209302325582</v>
@@ -943,13 +943,13 @@
         <v>421</v>
       </c>
       <c r="N4" t="n">
-        <v>1185</v>
+        <v>493</v>
       </c>
       <c r="O4" t="n">
-        <v>1382</v>
+        <v>690</v>
       </c>
       <c r="P4" t="n">
-        <v>0.550597609561753</v>
+        <v>0.2749003984063745</v>
       </c>
       <c r="Q4" t="n">
         <v>316</v>
@@ -970,25 +970,25 @@
         <v>0.0402390438247012</v>
       </c>
       <c r="W4" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="X4" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01792828685258964</v>
+        <v>0.02191235059760956</v>
       </c>
       <c r="Z4" t="n">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AA4" t="n">
-        <v>901</v>
+        <v>891</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3589641434262948</v>
+        <v>0.3549800796812749</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.8574529667149059</v>
+        <v>0.7144927536231884</v>
       </c>
       <c r="AD4" t="n">
         <v>0.4087968952134541</v>
@@ -997,13 +997,13 @@
         <v>0.3564356435643564</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.5111111111111111</v>
+        <v>0.509090909090909</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.4017758046614872</v>
+        <v>0.4006734006734007</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.714905933429812</v>
+        <v>1.428985507246377</v>
       </c>
       <c r="AI4" t="n">
         <v>0.7128712871287128</v>
@@ -1073,13 +1073,13 @@
         <v>11.07894736842105</v>
       </c>
       <c r="N5" t="n">
-        <v>31.18421052631579</v>
+        <v>12.97368421052632</v>
       </c>
       <c r="O5" t="n">
-        <v>36.36842105263158</v>
+        <v>18.15789473684211</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5505976095617531</v>
+        <v>0.2749003984063745</v>
       </c>
       <c r="Q5" t="n">
         <v>8.315789473684211</v>
@@ -1100,25 +1100,25 @@
         <v>0.0402390438247012</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6052631578947368</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="X5" t="n">
-        <v>1.184210526315789</v>
+        <v>1.447368421052632</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01792828685258964</v>
+        <v>0.02191235059760956</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.526315789473685</v>
+        <v>9.394736842105264</v>
       </c>
       <c r="AA5" t="n">
-        <v>23.71052631578947</v>
+        <v>23.44736842105263</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3589641434262948</v>
+        <v>0.3549800796812749</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.8574529667149059</v>
+        <v>0.7144927536231883</v>
       </c>
       <c r="AD5" t="n">
         <v>0.4087968952134541</v>
@@ -1127,13 +1127,13 @@
         <v>0.3564356435643564</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.5111111111111112</v>
+        <v>0.509090909090909</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.4017758046614873</v>
+        <v>0.4006734006734007</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.714905933429812</v>
+        <v>1.428985507246377</v>
       </c>
       <c r="AI5" t="n">
         <v>0.7128712871287128</v>
@@ -1498,13 +1498,13 @@
         <v>16</v>
       </c>
       <c r="Y8" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="Z8" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AB8" t="n">
         <v>17</v>
@@ -1525,22 +1525,22 @@
         <v>0.556</v>
       </c>
       <c r="AH8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AI8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.625</v>
+        <v>0.667</v>
       </c>
       <c r="AK8" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL8" t="n">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.333</v>
+        <v>0.321</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
@@ -1663,13 +1663,13 @@
         <v>16</v>
       </c>
       <c r="Y9" t="n">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="Z9" t="n">
-        <v>129</v>
+        <v>80</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.907</v>
+        <v>0.85</v>
       </c>
       <c r="AB9" t="n">
         <v>21</v>
@@ -1690,22 +1690,22 @@
         <v>0.6</v>
       </c>
       <c r="AH9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.429</v>
+        <v>0.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL9" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.329</v>
+        <v>0.313</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
@@ -1828,13 +1828,13 @@
         <v>22</v>
       </c>
       <c r="Y10" t="n">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="Z10" t="n">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.901</v>
+        <v>0.806</v>
       </c>
       <c r="AB10" t="n">
         <v>31</v>
@@ -1855,22 +1855,22 @@
         <v>0.571</v>
       </c>
       <c r="AH10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.364</v>
+        <v>0.417</v>
       </c>
       <c r="AK10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL10" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.278</v>
+        <v>0.27</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
@@ -1993,13 +1993,13 @@
         <v>11</v>
       </c>
       <c r="Y11" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="Z11" t="n">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.839</v>
+        <v>0.71</v>
       </c>
       <c r="AB11" t="n">
         <v>6</v>
@@ -2158,10 +2158,10 @@
         <v>4</v>
       </c>
       <c r="Y12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Z12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AA12" t="n">
         <v>1</v>
@@ -2188,7 +2188,7 @@
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
@@ -2197,7 +2197,7 @@
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
@@ -2323,13 +2323,13 @@
         <v>12</v>
       </c>
       <c r="Y13" t="n">
-        <v>114</v>
+        <v>39</v>
       </c>
       <c r="Z13" t="n">
-        <v>132</v>
+        <v>57</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.864</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AB13" t="n">
         <v>15</v>
@@ -2353,7 +2353,7 @@
         <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
@@ -2362,10 +2362,10 @@
         <v>21</v>
       </c>
       <c r="AL13" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.318</v>
+        <v>0.323</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
@@ -2488,13 +2488,13 @@
         <v>19</v>
       </c>
       <c r="Y14" t="n">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="Z14" t="n">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.9</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="AB14" t="n">
         <v>12</v>
@@ -2518,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
@@ -2527,10 +2527,10 @@
         <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.143</v>
+        <v>0.15</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
@@ -2653,13 +2653,13 @@
         <v>10</v>
       </c>
       <c r="Y15" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="Z15" t="n">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.844</v>
+        <v>0.75</v>
       </c>
       <c r="AB15" t="n">
         <v>19</v>
@@ -2683,19 +2683,19 @@
         <v>2</v>
       </c>
       <c r="AI15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AK15" t="n">
         <v>22</v>
       </c>
       <c r="AL15" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.379</v>
+        <v>0.386</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
@@ -2818,13 +2818,13 @@
         <v>6</v>
       </c>
       <c r="Y16" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="Z16" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.871</v>
+        <v>0.833</v>
       </c>
       <c r="AB16" t="n">
         <v>6</v>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
@@ -2857,10 +2857,10 @@
         <v>13</v>
       </c>
       <c r="AL16" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.295</v>
+        <v>0.302</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
@@ -2983,13 +2983,13 @@
         <v>44</v>
       </c>
       <c r="Y17" t="n">
-        <v>193</v>
+        <v>52</v>
       </c>
       <c r="Z17" t="n">
-        <v>211</v>
+        <v>70</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.915</v>
+        <v>0.743</v>
       </c>
       <c r="AB17" t="n">
         <v>53</v>
@@ -3010,22 +3010,22 @@
         <v>0.45</v>
       </c>
       <c r="AH17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.333</v>
+        <v>0.429</v>
       </c>
       <c r="AK17" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AL17" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.416</v>
+        <v>0.411</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
@@ -3148,13 +3148,13 @@
         <v>16</v>
       </c>
       <c r="Y18" t="n">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="Z18" t="n">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.844</v>
+        <v>0.636</v>
       </c>
       <c r="AB18" t="n">
         <v>29</v>
@@ -3313,13 +3313,13 @@
         <v>30</v>
       </c>
       <c r="Y19" t="n">
-        <v>148</v>
+        <v>43</v>
       </c>
       <c r="Z19" t="n">
-        <v>163</v>
+        <v>58</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.908</v>
+        <v>0.741</v>
       </c>
       <c r="AB19" t="n">
         <v>27</v>
@@ -3343,19 +3343,19 @@
         <v>2</v>
       </c>
       <c r="AI19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="AK19" t="n">
         <v>14</v>
       </c>
       <c r="AL19" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.255</v>
+        <v>0.259</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
@@ -3643,13 +3643,13 @@
         <v>6</v>
       </c>
       <c r="Y21" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="Z21" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.842</v>
+        <v>0.769</v>
       </c>
       <c r="AB21" t="n">
         <v>9</v>
@@ -3670,22 +3670,22 @@
         <v>0.333</v>
       </c>
       <c r="AH21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ21" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>33</v>
+      </c>
+      <c r="AM21" t="n">
         <v>0.333</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>12</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0.353</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
@@ -3808,13 +3808,13 @@
         <v>4</v>
       </c>
       <c r="Y22" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Z22" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.829</v>
+        <v>0.769</v>
       </c>
       <c r="AB22" t="n">
         <v>7</v>
@@ -4138,13 +4138,13 @@
         <v>7</v>
       </c>
       <c r="Y24" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="Z24" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.857</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="AB24" t="n">
         <v>14</v>
@@ -4165,22 +4165,22 @@
         <v>0.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="AK24" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL24" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.419</v>
+        <v>0.407</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
@@ -4798,13 +4798,13 @@
         <v>4</v>
       </c>
       <c r="Y28" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="Z28" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.824</v>
+        <v>0.5</v>
       </c>
       <c r="AB28" t="n">
         <v>6</v>
@@ -5128,13 +5128,13 @@
         <v>227</v>
       </c>
       <c r="Y30" t="n">
-        <v>1143</v>
+        <v>490</v>
       </c>
       <c r="Z30" t="n">
-        <v>1298</v>
+        <v>645</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.881</v>
+        <v>0.76</v>
       </c>
       <c r="AB30" t="n">
         <v>275</v>
@@ -5155,22 +5155,22 @@
         <v>0.442</v>
       </c>
       <c r="AH30" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="AI30" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.412</v>
+        <v>0.443</v>
       </c>
       <c r="AK30" t="n">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.338</v>
+        <v>0.334</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
@@ -5293,13 +5293,13 @@
         <v>246</v>
       </c>
       <c r="Y31" t="n">
-        <v>1185</v>
+        <v>493</v>
       </c>
       <c r="Z31" t="n">
-        <v>1382</v>
+        <v>690</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.857</v>
+        <v>0.714</v>
       </c>
       <c r="AB31" t="n">
         <v>316</v>
@@ -5320,22 +5320,22 @@
         <v>0.356</v>
       </c>
       <c r="AH31" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AI31" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.511</v>
+        <v>0.509</v>
       </c>
       <c r="AK31" t="n">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AL31" t="n">
-        <v>901</v>
+        <v>891</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.402</v>
+        <v>0.401</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
@@ -5517,13 +5517,13 @@
         <v>0.696</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.304</v>
+        <v>0.391</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.609</v>
+        <v>0.696</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AB33" t="n">
         <v>0.739</v>
@@ -5544,22 +5544,22 @@
         <v>0.556</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.217</v>
+        <v>0.348</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.348</v>
+        <v>0.522</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.625</v>
+        <v>0.667</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.043</v>
+        <v>1.913</v>
       </c>
       <c r="AL33" t="n">
-        <v>6.13</v>
+        <v>5.957</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.333</v>
+        <v>0.321</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
@@ -5682,13 +5682,13 @@
         <v>0.432</v>
       </c>
       <c r="Y34" t="n">
-        <v>3.162</v>
+        <v>1.838</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.486</v>
+        <v>2.162</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.907</v>
+        <v>0.85</v>
       </c>
       <c r="AB34" t="n">
         <v>0.5679999999999999</v>
@@ -5709,22 +5709,22 @@
         <v>0.6</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.081</v>
+        <v>0.135</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.189</v>
+        <v>0.27</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.429</v>
+        <v>0.5</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.622</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.892</v>
+        <v>1.811</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.329</v>
+        <v>0.313</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
@@ -5847,13 +5847,13 @@
         <v>0.71</v>
       </c>
       <c r="Y35" t="n">
-        <v>4.129</v>
+        <v>1.871</v>
       </c>
       <c r="Z35" t="n">
-        <v>4.581</v>
+        <v>2.323</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.901</v>
+        <v>0.806</v>
       </c>
       <c r="AB35" t="n">
         <v>1</v>
@@ -5874,22 +5874,22 @@
         <v>0.571</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.129</v>
+        <v>0.161</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.355</v>
+        <v>0.387</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.364</v>
+        <v>0.417</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.806</v>
+        <v>0.774</v>
       </c>
       <c r="AL35" t="n">
-        <v>2.903</v>
+        <v>2.871</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.278</v>
+        <v>0.27</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
@@ -6012,13 +6012,13 @@
         <v>0.367</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.567</v>
+        <v>0.733</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.867</v>
+        <v>1.033</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.839</v>
+        <v>0.71</v>
       </c>
       <c r="AB36" t="n">
         <v>0.2</v>
@@ -6177,10 +6177,10 @@
         <v>0.125</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.281</v>
+        <v>0.188</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.281</v>
+        <v>0.188</v>
       </c>
       <c r="AA37" t="n">
         <v>1</v>
@@ -6207,7 +6207,7 @@
         <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.031</v>
+        <v>0.062</v>
       </c>
       <c r="AJ37" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
         <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.125</v>
+        <v>0.094</v>
       </c>
       <c r="AM37" t="n">
         <v>0</v>
@@ -6342,13 +6342,13 @@
         <v>0.522</v>
       </c>
       <c r="Y38" t="n">
-        <v>4.957</v>
+        <v>1.696</v>
       </c>
       <c r="Z38" t="n">
-        <v>5.739</v>
+        <v>2.478</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.864</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AB38" t="n">
         <v>0.652</v>
@@ -6372,7 +6372,7 @@
         <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>0.043</v>
       </c>
       <c r="AJ38" t="n">
         <v>0</v>
@@ -6381,10 +6381,10 @@
         <v>0.913</v>
       </c>
       <c r="AL38" t="n">
-        <v>2.87</v>
+        <v>2.826</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.318</v>
+        <v>0.323</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
@@ -6507,13 +6507,13 @@
         <v>1.462</v>
       </c>
       <c r="Y39" t="n">
-        <v>6.231</v>
+        <v>3</v>
       </c>
       <c r="Z39" t="n">
-        <v>6.923</v>
+        <v>3.692</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.9</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="AB39" t="n">
         <v>0.923</v>
@@ -6537,7 +6537,7 @@
         <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.077</v>
+        <v>0.154</v>
       </c>
       <c r="AJ39" t="n">
         <v>0</v>
@@ -6546,10 +6546,10 @@
         <v>0.231</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.615</v>
+        <v>1.538</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.143</v>
+        <v>0.15</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
@@ -6672,13 +6672,13 @@
         <v>0.37</v>
       </c>
       <c r="Y40" t="n">
-        <v>2</v>
+        <v>1.111</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.37</v>
+        <v>1.481</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.844</v>
+        <v>0.75</v>
       </c>
       <c r="AB40" t="n">
         <v>0.704</v>
@@ -6702,19 +6702,19 @@
         <v>0.074</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.148</v>
+        <v>0.185</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AK40" t="n">
         <v>0.8149999999999999</v>
       </c>
       <c r="AL40" t="n">
-        <v>2.148</v>
+        <v>2.111</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.379</v>
+        <v>0.386</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
@@ -6837,13 +6837,13 @@
         <v>0.462</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.077</v>
+        <v>1.538</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.385</v>
+        <v>1.846</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.871</v>
+        <v>0.833</v>
       </c>
       <c r="AB41" t="n">
         <v>0.462</v>
@@ -6867,7 +6867,7 @@
         <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.154</v>
+        <v>0.231</v>
       </c>
       <c r="AJ41" t="n">
         <v>0</v>
@@ -6876,10 +6876,10 @@
         <v>1</v>
       </c>
       <c r="AL41" t="n">
-        <v>3.385</v>
+        <v>3.308</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.295</v>
+        <v>0.302</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
@@ -7002,13 +7002,13 @@
         <v>1.222</v>
       </c>
       <c r="Y42" t="n">
-        <v>5.361</v>
+        <v>1.444</v>
       </c>
       <c r="Z42" t="n">
-        <v>5.861</v>
+        <v>1.944</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.915</v>
+        <v>0.743</v>
       </c>
       <c r="AB42" t="n">
         <v>1.472</v>
@@ -7029,22 +7029,22 @@
         <v>0.45</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.111</v>
+        <v>0.167</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.333</v>
+        <v>0.389</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.333</v>
+        <v>0.429</v>
       </c>
       <c r="AK42" t="n">
-        <v>2.556</v>
+        <v>2.5</v>
       </c>
       <c r="AL42" t="n">
-        <v>6.139</v>
+        <v>6.083</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.416</v>
+        <v>0.411</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
@@ -7167,13 +7167,13 @@
         <v>0.432</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.757</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.081</v>
+        <v>0.892</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.844</v>
+        <v>0.636</v>
       </c>
       <c r="AB43" t="n">
         <v>0.784</v>
@@ -7332,13 +7332,13 @@
         <v>1.034</v>
       </c>
       <c r="Y44" t="n">
-        <v>5.103</v>
+        <v>1.483</v>
       </c>
       <c r="Z44" t="n">
-        <v>5.621</v>
+        <v>2</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.908</v>
+        <v>0.741</v>
       </c>
       <c r="AB44" t="n">
         <v>0.931</v>
@@ -7362,19 +7362,19 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.103</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="AK44" t="n">
         <v>0.483</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.897</v>
+        <v>1.862</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.255</v>
+        <v>0.259</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
@@ -7662,13 +7662,13 @@
         <v>0.24</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.28</v>
+        <v>0.8</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.52</v>
+        <v>1.04</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.842</v>
+        <v>0.769</v>
       </c>
       <c r="AB46" t="n">
         <v>0.36</v>
@@ -7689,22 +7689,22 @@
         <v>0.333</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="AI46" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="AJ46" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM46" t="n">
         <v>0.333</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>0.353</v>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
@@ -7827,13 +7827,13 @@
         <v>0.143</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.071</v>
+        <v>1.429</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.5</v>
+        <v>1.857</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.829</v>
+        <v>0.769</v>
       </c>
       <c r="AB47" t="n">
         <v>0.25</v>
@@ -8157,13 +8157,13 @@
         <v>0.184</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.632</v>
+        <v>0.474</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.737</v>
+        <v>0.579</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.857</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="AB49" t="n">
         <v>0.368</v>
@@ -8184,22 +8184,22 @@
         <v>0.5</v>
       </c>
       <c r="AH49" t="n">
-        <v>0.053</v>
+        <v>0.105</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.105</v>
+        <v>0.184</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="AK49" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.632</v>
       </c>
       <c r="AL49" t="n">
-        <v>1.632</v>
+        <v>1.553</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.419</v>
+        <v>0.407</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
@@ -8817,13 +8817,13 @@
         <v>0.8</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="Z53" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.824</v>
+        <v>0.5</v>
       </c>
       <c r="AB53" t="n">
         <v>1.2</v>
@@ -9147,13 +9147,13 @@
         <v>5.974</v>
       </c>
       <c r="Y55" t="n">
-        <v>30.079</v>
+        <v>12.895</v>
       </c>
       <c r="Z55" t="n">
-        <v>34.158</v>
+        <v>16.974</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.881</v>
+        <v>0.76</v>
       </c>
       <c r="AB55" t="n">
         <v>7.237</v>
@@ -9174,22 +9174,22 @@
         <v>0.442</v>
       </c>
       <c r="AH55" t="n">
-        <v>0.737</v>
+        <v>1.026</v>
       </c>
       <c r="AI55" t="n">
-        <v>1.789</v>
+        <v>2.316</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0.412</v>
+        <v>0.443</v>
       </c>
       <c r="AK55" t="n">
-        <v>8.895</v>
+        <v>8.605</v>
       </c>
       <c r="AL55" t="n">
-        <v>26.316</v>
+        <v>25.789</v>
       </c>
       <c r="AM55" t="n">
-        <v>0.338</v>
+        <v>0.334</v>
       </c>
       <c r="AN55" t="inlineStr">
         <is>
@@ -9312,13 +9312,13 @@
         <v>6.474</v>
       </c>
       <c r="Y56" t="n">
-        <v>31.184</v>
+        <v>12.974</v>
       </c>
       <c r="Z56" t="n">
-        <v>36.368</v>
+        <v>18.158</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.857</v>
+        <v>0.714</v>
       </c>
       <c r="AB56" t="n">
         <v>8.316000000000001</v>
@@ -9339,22 +9339,22 @@
         <v>0.356</v>
       </c>
       <c r="AH56" t="n">
-        <v>0.605</v>
+        <v>0.737</v>
       </c>
       <c r="AI56" t="n">
-        <v>1.184</v>
+        <v>1.447</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0.511</v>
+        <v>0.509</v>
       </c>
       <c r="AK56" t="n">
-        <v>9.526</v>
+        <v>9.395</v>
       </c>
       <c r="AL56" t="n">
-        <v>23.711</v>
+        <v>23.447</v>
       </c>
       <c r="AM56" t="n">
-        <v>0.402</v>
+        <v>0.401</v>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
